--- a/artfynd/A 5687-2022 artfynd.xlsx
+++ b/artfynd/A 5687-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121656363</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5687-2022 artfynd.xlsx
+++ b/artfynd/A 5687-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121656363</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5687-2022 artfynd.xlsx
+++ b/artfynd/A 5687-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+          <t>Enviro Planning, Pia Edfors, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
